--- a/Sales_Analysis.xlsx
+++ b/Sales_Analysis.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\My projects\Excel_Project\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\My projects\Excel_Project\Sales_AnalysisProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{312F3AE1-DA60-4616-BDC8-54EA25AFC7B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{652B7A00-629B-491D-A507-914093240A95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{01602610-4AEF-42F2-B3B4-D768E7A78288}"/>
   </bookViews>
@@ -21,7 +21,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="8" r:id="rId3"/>
+    <pivotCache cacheId="0" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -1006,6 +1006,7 @@
     </font>
     <font>
       <sz val="8"/>
+      <color rgb="FF000000"/>
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
@@ -1092,9 +1093,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1120,14 +1121,14 @@
         <dxf>
           <fill>
             <patternFill>
-              <bgColor theme="7" tint="0.79998168889431442"/>
+              <bgColor theme="7" tint="0.59996337778862885"/>
             </patternFill>
           </fill>
         </dxf>
         <dxf>
           <fill>
             <patternFill>
-              <bgColor theme="7" tint="0.59996337778862885"/>
+              <bgColor theme="7" tint="0.79998168889431442"/>
             </patternFill>
           </fill>
         </dxf>
@@ -1153,8 +1154,8 @@
           <x14:slicerStyleElements>
             <x14:slicerStyleElement type="unselectedItemWithData" dxfId="3"/>
             <x14:slicerStyleElement type="selectedItemWithData" dxfId="2"/>
-            <x14:slicerStyleElement type="hoveredUnselectedItemWithData" dxfId="0"/>
-            <x14:slicerStyleElement type="hoveredSelectedItemWithData" dxfId="1"/>
+            <x14:slicerStyleElement type="hoveredUnselectedItemWithData" dxfId="1"/>
+            <x14:slicerStyleElement type="hoveredSelectedItemWithData" dxfId="0"/>
           </x14:slicerStyleElements>
         </x14:slicerStyle>
       </x14:slicerStyles>
@@ -1340,19 +1341,19 @@
               <c:strCache>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>Anita Dixit</c:v>
+                  <c:v>Janardan Mishra</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Daleep Singh</c:v>
+                  <c:v>Kamini Kumar</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Jagdish Chandra</c:v>
+                  <c:v>Rekha Agarwal</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Nandu Kumar</c:v>
+                  <c:v>Saroj Parita</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>Rachita Anupam</c:v>
+                  <c:v>Shivji Prasad</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1364,19 +1365,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>316</c:v>
+                  <c:v>355</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>316</c:v>
+                  <c:v>322</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>389</c:v>
+                  <c:v>350</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>317</c:v>
+                  <c:v>353</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>385</c:v>
+                  <c:v>301</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1583,8 +1584,7 @@
           </a:effectLst>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="6"/>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -1645,6 +1645,96 @@
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+              <a:prstClr val="black">
+                <a:alpha val="20000"/>
+              </a:prstClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+              <a:prstClr val="black">
+                <a:alpha val="20000"/>
+              </a:prstClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+              <a:prstClr val="black">
+                <a:alpha val="20000"/>
+              </a:prstClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+              <a:prstClr val="black">
+                <a:alpha val="20000"/>
+              </a:prstClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="5"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+              <a:prstClr val="black">
+                <a:alpha val="20000"/>
+              </a:prstClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+      </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
       <c:layout/>
@@ -1682,6 +1772,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-B94B-4C7B-9AA4-7DB439F2DA64}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -1701,6 +1796,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-B94B-4C7B-9AA4-7DB439F2DA64}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
@@ -1720,6 +1820,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-B94B-4C7B-9AA4-7DB439F2DA64}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="3"/>
@@ -1739,6 +1844,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-B94B-4C7B-9AA4-7DB439F2DA64}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="4"/>
@@ -1758,6 +1868,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000009-B94B-4C7B-9AA4-7DB439F2DA64}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dLbls>
             <c:spPr>
@@ -2000,6 +2115,9 @@
       <c:pivotFmt>
         <c:idx val="0"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -2208,19 +2326,19 @@
               <c:strCache>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>Arun Kumar</c:v>
+                  <c:v>Anjali Deoram</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Owais Mohd</c:v>
+                  <c:v>Lilly Lucy</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Rajesh Kumar</c:v>
+                  <c:v>Mehnaz Khan</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Sheena Joseph</c:v>
+                  <c:v>Partha Sarathi</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>Sudhir Kumar</c:v>
+                  <c:v>Raji Abraham</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2232,19 +2350,19 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>0.63400000000000001</c:v>
+                  <c:v>0.56600000000000006</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.58400000000000007</c:v>
+                  <c:v>0.59000000000000008</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.61599999999999999</c:v>
+                  <c:v>0.57000000000000006</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.63400000000000001</c:v>
+                  <c:v>0.54200000000000004</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.60199999999999998</c:v>
+                  <c:v>0.622</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4165,7 +4283,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp3.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$G$1" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$G$1" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp4.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4295,8 +4413,8 @@
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="5" name="Region">
@@ -4319,7 +4437,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -4446,7 +4564,7 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1026" name="Check Box 2" hidden="1">
+            <xdr:cNvPr id="1026" name="Check Box 2" descr="Dashbord 1" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1026"/>
@@ -4601,13 +4719,13 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1027" name="Check Box 3" hidden="1">
+            <xdr:cNvPr id="1027" name="Check Box 3" descr="Dashbord 1" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1027"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002040000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4756,13 +4874,13 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1028" name="Check Box 4" hidden="1">
+            <xdr:cNvPr id="1028" name="Check Box 4" descr="Dashbord 1" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1028"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002040000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4911,13 +5029,13 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1029" name="Check Box 5" hidden="1">
+            <xdr:cNvPr id="1029" name="Check Box 5" descr="Dashbord 1" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1029"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002040000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -7165,7 +7283,460 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B2D424B4-A147-4BFF-A358-F9B5E60D24E2}" name="PivotTable8" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2" rowHeaderCaption="Sales Excutive">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E3BAEC30-0139-4A47-9C31-1D63B4861E08}" name="PivotTable6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Sales Excutive ">
+  <location ref="D3:E8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="12">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" measureFilter="1">
+      <items count="142">
+        <item x="140"/>
+        <item x="139"/>
+        <item x="138"/>
+        <item x="137"/>
+        <item x="136"/>
+        <item x="135"/>
+        <item x="134"/>
+        <item x="133"/>
+        <item x="132"/>
+        <item x="131"/>
+        <item x="130"/>
+        <item x="129"/>
+        <item x="128"/>
+        <item x="4"/>
+        <item x="127"/>
+        <item x="2"/>
+        <item x="126"/>
+        <item x="125"/>
+        <item x="124"/>
+        <item x="123"/>
+        <item x="122"/>
+        <item x="121"/>
+        <item x="120"/>
+        <item x="119"/>
+        <item x="118"/>
+        <item x="117"/>
+        <item x="116"/>
+        <item x="115"/>
+        <item x="114"/>
+        <item x="113"/>
+        <item x="112"/>
+        <item x="111"/>
+        <item x="110"/>
+        <item x="109"/>
+        <item x="108"/>
+        <item x="107"/>
+        <item x="106"/>
+        <item x="105"/>
+        <item x="104"/>
+        <item x="103"/>
+        <item x="102"/>
+        <item x="101"/>
+        <item x="100"/>
+        <item x="99"/>
+        <item x="98"/>
+        <item x="97"/>
+        <item x="96"/>
+        <item x="95"/>
+        <item x="94"/>
+        <item x="93"/>
+        <item x="92"/>
+        <item x="91"/>
+        <item x="90"/>
+        <item x="89"/>
+        <item x="88"/>
+        <item x="87"/>
+        <item x="86"/>
+        <item x="85"/>
+        <item x="84"/>
+        <item x="83"/>
+        <item x="82"/>
+        <item x="81"/>
+        <item x="80"/>
+        <item x="79"/>
+        <item x="78"/>
+        <item x="77"/>
+        <item x="76"/>
+        <item x="75"/>
+        <item x="74"/>
+        <item x="73"/>
+        <item x="72"/>
+        <item x="71"/>
+        <item x="70"/>
+        <item x="69"/>
+        <item x="68"/>
+        <item x="67"/>
+        <item x="66"/>
+        <item x="65"/>
+        <item x="64"/>
+        <item x="63"/>
+        <item x="62"/>
+        <item x="61"/>
+        <item x="0"/>
+        <item x="60"/>
+        <item x="59"/>
+        <item x="58"/>
+        <item x="57"/>
+        <item x="56"/>
+        <item x="55"/>
+        <item x="54"/>
+        <item x="53"/>
+        <item x="52"/>
+        <item x="51"/>
+        <item x="50"/>
+        <item x="49"/>
+        <item x="48"/>
+        <item x="47"/>
+        <item x="46"/>
+        <item x="45"/>
+        <item x="44"/>
+        <item x="43"/>
+        <item x="42"/>
+        <item x="41"/>
+        <item x="40"/>
+        <item x="39"/>
+        <item x="38"/>
+        <item x="37"/>
+        <item x="36"/>
+        <item x="35"/>
+        <item x="34"/>
+        <item x="33"/>
+        <item x="32"/>
+        <item x="31"/>
+        <item x="30"/>
+        <item x="29"/>
+        <item x="28"/>
+        <item x="27"/>
+        <item x="26"/>
+        <item x="25"/>
+        <item x="24"/>
+        <item x="23"/>
+        <item x="22"/>
+        <item x="21"/>
+        <item x="20"/>
+        <item x="19"/>
+        <item x="18"/>
+        <item x="17"/>
+        <item x="16"/>
+        <item x="15"/>
+        <item x="14"/>
+        <item x="13"/>
+        <item x="12"/>
+        <item x="11"/>
+        <item x="10"/>
+        <item x="9"/>
+        <item x="8"/>
+        <item x="7"/>
+        <item x="6"/>
+        <item x="5"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="9">
+        <item h="1" x="3"/>
+        <item h="1" x="1"/>
+        <item h="1" x="0"/>
+        <item h="1" x="2"/>
+        <item x="5"/>
+        <item h="1" x="4"/>
+        <item h="1" x="6"/>
+        <item h="1" x="7"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="10" showAll="0"/>
+    <pivotField numFmtId="10" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="49"/>
+    </i>
+    <i>
+      <x v="57"/>
+    </i>
+    <i>
+      <x v="73"/>
+    </i>
+    <i>
+      <x v="90"/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Total Sales " fld="8" baseField="1" baseItem="3"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleMedium18" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <filters count="1">
+    <filter fld="1" type="count" evalOrder="-1" id="2" iMeasureFld="0">
+      <autoFilter ref="A1">
+        <filterColumn colId="0">
+          <top10 top="0" val="5" filterVal="5"/>
+        </filterColumn>
+      </autoFilter>
+    </filter>
+  </filters>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{242CF08D-5AD9-4E2F-8534-F3E9A4812886}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3" rowHeaderCaption="Sales Excutive ">
+  <location ref="A3:B8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="12">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" measureFilter="1">
+      <items count="142">
+        <item x="140"/>
+        <item x="139"/>
+        <item x="138"/>
+        <item x="137"/>
+        <item x="136"/>
+        <item x="135"/>
+        <item x="134"/>
+        <item x="133"/>
+        <item x="132"/>
+        <item x="131"/>
+        <item x="130"/>
+        <item x="129"/>
+        <item x="128"/>
+        <item x="4"/>
+        <item x="127"/>
+        <item x="2"/>
+        <item x="126"/>
+        <item x="125"/>
+        <item x="124"/>
+        <item x="123"/>
+        <item x="122"/>
+        <item x="121"/>
+        <item x="120"/>
+        <item x="119"/>
+        <item x="118"/>
+        <item x="117"/>
+        <item x="116"/>
+        <item x="115"/>
+        <item x="114"/>
+        <item x="113"/>
+        <item x="112"/>
+        <item x="111"/>
+        <item x="110"/>
+        <item x="109"/>
+        <item x="108"/>
+        <item x="107"/>
+        <item x="106"/>
+        <item x="105"/>
+        <item x="104"/>
+        <item x="103"/>
+        <item x="102"/>
+        <item x="101"/>
+        <item x="100"/>
+        <item x="99"/>
+        <item x="98"/>
+        <item x="97"/>
+        <item x="96"/>
+        <item x="95"/>
+        <item x="94"/>
+        <item x="93"/>
+        <item x="92"/>
+        <item x="91"/>
+        <item x="90"/>
+        <item x="89"/>
+        <item x="88"/>
+        <item x="87"/>
+        <item x="86"/>
+        <item x="85"/>
+        <item x="84"/>
+        <item x="83"/>
+        <item x="82"/>
+        <item x="81"/>
+        <item x="80"/>
+        <item x="79"/>
+        <item x="78"/>
+        <item x="77"/>
+        <item x="76"/>
+        <item x="75"/>
+        <item x="74"/>
+        <item x="73"/>
+        <item x="72"/>
+        <item x="71"/>
+        <item x="70"/>
+        <item x="69"/>
+        <item x="68"/>
+        <item x="67"/>
+        <item x="66"/>
+        <item x="65"/>
+        <item x="64"/>
+        <item x="63"/>
+        <item x="62"/>
+        <item x="61"/>
+        <item x="0"/>
+        <item x="60"/>
+        <item x="59"/>
+        <item x="58"/>
+        <item x="57"/>
+        <item x="56"/>
+        <item x="55"/>
+        <item x="54"/>
+        <item x="53"/>
+        <item x="52"/>
+        <item x="51"/>
+        <item x="50"/>
+        <item x="49"/>
+        <item x="48"/>
+        <item x="47"/>
+        <item x="46"/>
+        <item x="45"/>
+        <item x="44"/>
+        <item x="43"/>
+        <item x="42"/>
+        <item x="41"/>
+        <item x="40"/>
+        <item x="39"/>
+        <item x="38"/>
+        <item x="37"/>
+        <item x="36"/>
+        <item x="35"/>
+        <item x="34"/>
+        <item x="33"/>
+        <item x="32"/>
+        <item x="31"/>
+        <item x="30"/>
+        <item x="29"/>
+        <item x="28"/>
+        <item x="27"/>
+        <item x="26"/>
+        <item x="25"/>
+        <item x="24"/>
+        <item x="23"/>
+        <item x="22"/>
+        <item x="21"/>
+        <item x="20"/>
+        <item x="19"/>
+        <item x="18"/>
+        <item x="17"/>
+        <item x="16"/>
+        <item x="15"/>
+        <item x="14"/>
+        <item x="13"/>
+        <item x="12"/>
+        <item x="11"/>
+        <item x="10"/>
+        <item x="9"/>
+        <item x="8"/>
+        <item x="7"/>
+        <item x="6"/>
+        <item x="5"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="9">
+        <item h="1" x="3"/>
+        <item h="1" x="1"/>
+        <item h="1" x="0"/>
+        <item h="1" x="2"/>
+        <item x="5"/>
+        <item h="1" x="4"/>
+        <item h="1" x="6"/>
+        <item h="1" x="7"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="10" showAll="0"/>
+    <pivotField numFmtId="10" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x v="33"/>
+    </i>
+    <i>
+      <x v="41"/>
+    </i>
+    <i>
+      <x v="98"/>
+    </i>
+    <i>
+      <x v="114"/>
+    </i>
+    <i>
+      <x v="122"/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Total Sales " fld="8" baseField="1" baseItem="3"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleMedium18" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <filters count="1">
+    <filter fld="1" type="count" evalOrder="-1" id="1" iMeasureFld="0">
+      <autoFilter ref="A1">
+        <filterColumn colId="0">
+          <top10 val="5" filterVal="5"/>
+        </filterColumn>
+      </autoFilter>
+    </filter>
+  </filters>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B2D424B4-A147-4BFF-A358-F9B5E60D24E2}" name="PivotTable8" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2" rowHeaderCaption="Sales Excutive">
   <location ref="J3:K8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField showAll="0"/>
@@ -7321,10 +7892,10 @@
         <item h="1" x="1"/>
         <item h="1" x="0"/>
         <item h="1" x="2"/>
-        <item h="1" x="5"/>
+        <item x="5"/>
         <item h="1" x="4"/>
         <item h="1" x="6"/>
-        <item x="7"/>
+        <item h="1" x="7"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -7343,19 +7914,19 @@
   </rowFields>
   <rowItems count="5">
     <i>
-      <x v="14"/>
+      <x v="7"/>
     </i>
     <i>
-      <x v="71"/>
+      <x v="49"/>
     </i>
     <i>
-      <x v="88"/>
+      <x v="57"/>
     </i>
     <i>
-      <x v="120"/>
+      <x v="73"/>
     </i>
     <i>
-      <x v="128"/>
+      <x v="90"/>
     </i>
   </rowItems>
   <colItems count="1">
@@ -7396,8 +7967,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{591D3B58-17E1-4F00-9951-4777ECE4E74D}" name="PivotTable7" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3" rowHeaderCaption="Sales Excutive">
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{591D3B58-17E1-4F00-9951-4777ECE4E74D}" name="PivotTable7" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3" rowHeaderCaption="Sales Excutive">
   <location ref="G3:H8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField showAll="0"/>
@@ -7596,7 +8167,7 @@
   <dataFields count="1">
     <dataField name="Target Hit % " fld="10" baseField="1" baseItem="3" numFmtId="10"/>
   </dataFields>
-  <chartFormats count="1">
+  <chartFormats count="6">
     <chartFormat chart="0" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
@@ -7606,461 +8177,68 @@
         </references>
       </pivotArea>
     </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleMedium19" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <filters count="1">
-    <filter fld="1" type="count" evalOrder="-1" id="1" iMeasureFld="0">
-      <autoFilter ref="A1">
-        <filterColumn colId="0">
-          <top10 val="5" filterVal="5"/>
-        </filterColumn>
-      </autoFilter>
-    </filter>
-  </filters>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E3BAEC30-0139-4A47-9C31-1D63B4861E08}" name="PivotTable6" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Sales Excutive ">
-  <location ref="D3:E8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="12">
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0" measureFilter="1">
-      <items count="142">
-        <item x="140"/>
-        <item x="139"/>
-        <item x="138"/>
-        <item x="137"/>
-        <item x="136"/>
-        <item x="135"/>
-        <item x="134"/>
-        <item x="133"/>
-        <item x="132"/>
-        <item x="131"/>
-        <item x="130"/>
-        <item x="129"/>
-        <item x="128"/>
-        <item x="4"/>
-        <item x="127"/>
-        <item x="2"/>
-        <item x="126"/>
-        <item x="125"/>
-        <item x="124"/>
-        <item x="123"/>
-        <item x="122"/>
-        <item x="121"/>
-        <item x="120"/>
-        <item x="119"/>
-        <item x="118"/>
-        <item x="117"/>
-        <item x="116"/>
-        <item x="115"/>
-        <item x="114"/>
-        <item x="113"/>
-        <item x="112"/>
-        <item x="111"/>
-        <item x="110"/>
-        <item x="109"/>
-        <item x="108"/>
-        <item x="107"/>
-        <item x="106"/>
-        <item x="105"/>
-        <item x="104"/>
-        <item x="103"/>
-        <item x="102"/>
-        <item x="101"/>
-        <item x="100"/>
-        <item x="99"/>
-        <item x="98"/>
-        <item x="97"/>
-        <item x="96"/>
-        <item x="95"/>
-        <item x="94"/>
-        <item x="93"/>
-        <item x="92"/>
-        <item x="91"/>
-        <item x="90"/>
-        <item x="89"/>
-        <item x="88"/>
-        <item x="87"/>
-        <item x="86"/>
-        <item x="85"/>
-        <item x="84"/>
-        <item x="83"/>
-        <item x="82"/>
-        <item x="81"/>
-        <item x="80"/>
-        <item x="79"/>
-        <item x="78"/>
-        <item x="77"/>
-        <item x="76"/>
-        <item x="75"/>
-        <item x="74"/>
-        <item x="73"/>
-        <item x="72"/>
-        <item x="71"/>
-        <item x="70"/>
-        <item x="69"/>
-        <item x="68"/>
-        <item x="67"/>
-        <item x="66"/>
-        <item x="65"/>
-        <item x="64"/>
-        <item x="63"/>
-        <item x="62"/>
-        <item x="61"/>
-        <item x="0"/>
-        <item x="60"/>
-        <item x="59"/>
-        <item x="58"/>
-        <item x="57"/>
-        <item x="56"/>
-        <item x="55"/>
-        <item x="54"/>
-        <item x="53"/>
-        <item x="52"/>
-        <item x="51"/>
-        <item x="50"/>
-        <item x="49"/>
-        <item x="48"/>
-        <item x="47"/>
-        <item x="46"/>
-        <item x="45"/>
-        <item x="44"/>
-        <item x="43"/>
-        <item x="42"/>
-        <item x="41"/>
-        <item x="40"/>
-        <item x="39"/>
-        <item x="38"/>
-        <item x="37"/>
-        <item x="36"/>
-        <item x="35"/>
-        <item x="34"/>
-        <item x="33"/>
-        <item x="32"/>
-        <item x="31"/>
-        <item x="30"/>
-        <item x="29"/>
-        <item x="28"/>
-        <item x="27"/>
-        <item x="26"/>
-        <item x="25"/>
-        <item x="24"/>
-        <item x="23"/>
-        <item x="22"/>
-        <item x="21"/>
-        <item x="20"/>
-        <item x="19"/>
-        <item x="18"/>
-        <item x="17"/>
-        <item x="16"/>
-        <item x="15"/>
-        <item x="14"/>
-        <item x="13"/>
-        <item x="12"/>
-        <item x="11"/>
-        <item x="10"/>
-        <item x="9"/>
-        <item x="8"/>
-        <item x="7"/>
-        <item x="6"/>
-        <item x="5"/>
-        <item x="3"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="9">
-        <item h="1" x="3"/>
-        <item h="1" x="1"/>
-        <item h="1" x="0"/>
-        <item h="1" x="2"/>
-        <item h="1" x="5"/>
-        <item h="1" x="4"/>
-        <item h="1" x="6"/>
-        <item x="7"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="10" showAll="0"/>
-    <pivotField numFmtId="10" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="1"/>
-  </rowFields>
-  <rowItems count="5">
-    <i>
-      <x v="14"/>
-    </i>
-    <i>
-      <x v="71"/>
-    </i>
-    <i>
-      <x v="88"/>
-    </i>
-    <i>
-      <x v="120"/>
-    </i>
-    <i>
-      <x v="128"/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Total Sales " fld="8" baseField="1" baseItem="3"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleMedium18" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <filters count="1">
-    <filter fld="1" type="count" evalOrder="-1" id="2" iMeasureFld="0">
-      <autoFilter ref="A1">
-        <filterColumn colId="0">
-          <top10 top="0" val="5" filterVal="5"/>
-        </filterColumn>
-      </autoFilter>
-    </filter>
-  </filters>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{242CF08D-5AD9-4E2F-8534-F3E9A4812886}" name="PivotTable5" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3" rowHeaderCaption="Sales Excutive ">
-  <location ref="A3:B8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="12">
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0" measureFilter="1">
-      <items count="142">
-        <item x="140"/>
-        <item x="139"/>
-        <item x="138"/>
-        <item x="137"/>
-        <item x="136"/>
-        <item x="135"/>
-        <item x="134"/>
-        <item x="133"/>
-        <item x="132"/>
-        <item x="131"/>
-        <item x="130"/>
-        <item x="129"/>
-        <item x="128"/>
-        <item x="4"/>
-        <item x="127"/>
-        <item x="2"/>
-        <item x="126"/>
-        <item x="125"/>
-        <item x="124"/>
-        <item x="123"/>
-        <item x="122"/>
-        <item x="121"/>
-        <item x="120"/>
-        <item x="119"/>
-        <item x="118"/>
-        <item x="117"/>
-        <item x="116"/>
-        <item x="115"/>
-        <item x="114"/>
-        <item x="113"/>
-        <item x="112"/>
-        <item x="111"/>
-        <item x="110"/>
-        <item x="109"/>
-        <item x="108"/>
-        <item x="107"/>
-        <item x="106"/>
-        <item x="105"/>
-        <item x="104"/>
-        <item x="103"/>
-        <item x="102"/>
-        <item x="101"/>
-        <item x="100"/>
-        <item x="99"/>
-        <item x="98"/>
-        <item x="97"/>
-        <item x="96"/>
-        <item x="95"/>
-        <item x="94"/>
-        <item x="93"/>
-        <item x="92"/>
-        <item x="91"/>
-        <item x="90"/>
-        <item x="89"/>
-        <item x="88"/>
-        <item x="87"/>
-        <item x="86"/>
-        <item x="85"/>
-        <item x="84"/>
-        <item x="83"/>
-        <item x="82"/>
-        <item x="81"/>
-        <item x="80"/>
-        <item x="79"/>
-        <item x="78"/>
-        <item x="77"/>
-        <item x="76"/>
-        <item x="75"/>
-        <item x="74"/>
-        <item x="73"/>
-        <item x="72"/>
-        <item x="71"/>
-        <item x="70"/>
-        <item x="69"/>
-        <item x="68"/>
-        <item x="67"/>
-        <item x="66"/>
-        <item x="65"/>
-        <item x="64"/>
-        <item x="63"/>
-        <item x="62"/>
-        <item x="61"/>
-        <item x="0"/>
-        <item x="60"/>
-        <item x="59"/>
-        <item x="58"/>
-        <item x="57"/>
-        <item x="56"/>
-        <item x="55"/>
-        <item x="54"/>
-        <item x="53"/>
-        <item x="52"/>
-        <item x="51"/>
-        <item x="50"/>
-        <item x="49"/>
-        <item x="48"/>
-        <item x="47"/>
-        <item x="46"/>
-        <item x="45"/>
-        <item x="44"/>
-        <item x="43"/>
-        <item x="42"/>
-        <item x="41"/>
-        <item x="40"/>
-        <item x="39"/>
-        <item x="38"/>
-        <item x="37"/>
-        <item x="36"/>
-        <item x="35"/>
-        <item x="34"/>
-        <item x="33"/>
-        <item x="32"/>
-        <item x="31"/>
-        <item x="30"/>
-        <item x="29"/>
-        <item x="28"/>
-        <item x="27"/>
-        <item x="26"/>
-        <item x="25"/>
-        <item x="24"/>
-        <item x="23"/>
-        <item x="22"/>
-        <item x="21"/>
-        <item x="20"/>
-        <item x="19"/>
-        <item x="18"/>
-        <item x="17"/>
-        <item x="16"/>
-        <item x="15"/>
-        <item x="14"/>
-        <item x="13"/>
-        <item x="12"/>
-        <item x="11"/>
-        <item x="10"/>
-        <item x="9"/>
-        <item x="8"/>
-        <item x="7"/>
-        <item x="6"/>
-        <item x="5"/>
-        <item x="3"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="9">
-        <item h="1" x="3"/>
-        <item h="1" x="1"/>
-        <item h="1" x="0"/>
-        <item h="1" x="2"/>
-        <item h="1" x="5"/>
-        <item h="1" x="4"/>
-        <item h="1" x="6"/>
-        <item x="7"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="10" showAll="0"/>
-    <pivotField numFmtId="10" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="1"/>
-  </rowFields>
-  <rowItems count="5">
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="23"/>
-    </i>
-    <i>
-      <x v="31"/>
-    </i>
-    <i>
-      <x v="63"/>
-    </i>
-    <i>
-      <x v="79"/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Total Sales " fld="8" baseField="1" baseItem="3"/>
-  </dataFields>
-  <chartFormats count="1">
-    <chartFormat chart="0" format="0" series="1">
+    <chartFormat chart="0" format="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
+        <references count="2">
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="2">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="15"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="3">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="31"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="4">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="59"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="5">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="79"/>
           </reference>
         </references>
       </pivotArea>
     </chartFormat>
   </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleMedium18" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <pivotTableStyleInfo name="PivotStyleMedium19" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <filters count="1">
     <filter fld="1" type="count" evalOrder="-1" id="1" iMeasureFld="0">
       <autoFilter ref="A1">
@@ -8095,10 +8273,10 @@
         <i x="1"/>
         <i x="0"/>
         <i x="2"/>
-        <i x="5"/>
+        <i x="5" s="1"/>
         <i x="4"/>
         <i x="6"/>
-        <i x="7" s="1"/>
+        <i x="7"/>
       </items>
     </tabular>
   </data>
@@ -8433,24 +8611,24 @@
         <v>1</v>
       </c>
       <c r="G1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="13"/>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
+      <c r="A2" s="12"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="12"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
@@ -8459,21 +8637,21 @@
       <c r="B3" t="s">
         <v>303</v>
       </c>
-      <c r="C3" s="13"/>
+      <c r="C3" s="12"/>
       <c r="D3" s="9" t="s">
         <v>302</v>
       </c>
       <c r="E3" t="s">
         <v>303</v>
       </c>
-      <c r="F3" s="13"/>
+      <c r="F3" s="12"/>
       <c r="G3" s="9" t="s">
         <v>304</v>
       </c>
       <c r="H3" t="s">
         <v>305</v>
       </c>
-      <c r="I3" s="13"/>
+      <c r="I3" s="12"/>
       <c r="J3" s="9" t="s">
         <v>304</v>
       </c>
@@ -8483,382 +8661,382 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
-        <v>291</v>
-      </c>
-      <c r="B4" s="11">
-        <v>316</v>
-      </c>
-      <c r="C4" s="13"/>
+        <v>239</v>
+      </c>
+      <c r="B4" s="13">
+        <v>355</v>
+      </c>
+      <c r="C4" s="12"/>
       <c r="D4" s="10" t="s">
-        <v>275</v>
-      </c>
-      <c r="E4" s="11">
-        <v>183</v>
-      </c>
-      <c r="F4" s="13"/>
+        <v>287</v>
+      </c>
+      <c r="E4" s="13">
+        <v>217</v>
+      </c>
+      <c r="F4" s="12"/>
       <c r="G4" s="10" t="s">
         <v>295</v>
       </c>
-      <c r="H4" s="12">
+      <c r="H4" s="11">
         <v>0.76400000000000001</v>
       </c>
-      <c r="I4" s="13"/>
+      <c r="I4" s="12"/>
       <c r="J4" s="10" t="s">
-        <v>275</v>
-      </c>
-      <c r="K4" s="12">
-        <v>0.63400000000000001</v>
+        <v>287</v>
+      </c>
+      <c r="K4" s="11">
+        <v>0.56600000000000006</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
-        <v>259</v>
-      </c>
-      <c r="B5" s="11">
-        <v>316</v>
-      </c>
-      <c r="C5" s="13"/>
+        <v>223</v>
+      </c>
+      <c r="B5" s="13">
+        <v>322</v>
+      </c>
+      <c r="C5" s="12"/>
       <c r="D5" s="10" t="s">
-        <v>163</v>
-      </c>
-      <c r="E5" s="11">
-        <v>208</v>
-      </c>
-      <c r="F5" s="13"/>
+        <v>207</v>
+      </c>
+      <c r="E5" s="13">
+        <v>205</v>
+      </c>
+      <c r="F5" s="12"/>
       <c r="G5" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="H5" s="12">
+      <c r="H5" s="11">
         <v>0.75800000000000001</v>
       </c>
-      <c r="I5" s="13"/>
+      <c r="I5" s="12"/>
       <c r="J5" s="10" t="s">
-        <v>163</v>
-      </c>
-      <c r="K5" s="12">
-        <v>0.58400000000000007</v>
+        <v>207</v>
+      </c>
+      <c r="K5" s="11">
+        <v>0.59000000000000008</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
-        <v>243</v>
-      </c>
-      <c r="B6" s="11">
-        <v>389</v>
-      </c>
-      <c r="C6" s="13"/>
+        <v>111</v>
+      </c>
+      <c r="B6" s="13">
+        <v>350</v>
+      </c>
+      <c r="C6" s="12"/>
       <c r="D6" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="E6" s="11">
-        <v>192</v>
-      </c>
-      <c r="F6" s="13"/>
+        <v>191</v>
+      </c>
+      <c r="E6" s="13">
+        <v>215</v>
+      </c>
+      <c r="F6" s="12"/>
       <c r="G6" s="10" t="s">
         <v>243</v>
       </c>
-      <c r="H6" s="12">
+      <c r="H6" s="11">
         <v>0.77800000000000002</v>
       </c>
-      <c r="I6" s="13"/>
+      <c r="I6" s="12"/>
       <c r="J6" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="K6" s="12">
-        <v>0.61599999999999999</v>
+        <v>191</v>
+      </c>
+      <c r="K6" s="11">
+        <v>0.57000000000000006</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="B7" s="11">
-        <v>317</v>
-      </c>
-      <c r="C7" s="13"/>
+        <v>79</v>
+      </c>
+      <c r="B7" s="13">
+        <v>353</v>
+      </c>
+      <c r="C7" s="12"/>
       <c r="D7" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="E7" s="11">
-        <v>183</v>
-      </c>
-      <c r="F7" s="13"/>
+        <v>159</v>
+      </c>
+      <c r="E7" s="13">
+        <v>229</v>
+      </c>
+      <c r="F7" s="12"/>
       <c r="G7" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="H7" s="12">
+      <c r="H7" s="11">
         <v>0.76800000000000002</v>
       </c>
-      <c r="I7" s="13"/>
+      <c r="I7" s="12"/>
       <c r="J7" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="K7" s="12">
-        <v>0.63400000000000001</v>
+        <v>159</v>
+      </c>
+      <c r="K7" s="11">
+        <v>0.54200000000000004</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="10" t="s">
-        <v>147</v>
-      </c>
-      <c r="B8" s="11">
-        <v>385</v>
-      </c>
-      <c r="C8" s="13"/>
+        <v>63</v>
+      </c>
+      <c r="B8" s="13">
+        <v>301</v>
+      </c>
+      <c r="C8" s="12"/>
       <c r="D8" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="E8" s="11">
-        <v>199</v>
-      </c>
-      <c r="F8" s="13"/>
+        <v>127</v>
+      </c>
+      <c r="E8" s="13">
+        <v>189</v>
+      </c>
+      <c r="F8" s="12"/>
       <c r="G8" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="H8" s="12">
+      <c r="H8" s="11">
         <v>0.77</v>
       </c>
-      <c r="I8" s="13"/>
+      <c r="I8" s="12"/>
       <c r="J8" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="K8" s="12">
-        <v>0.60199999999999998</v>
+        <v>127</v>
+      </c>
+      <c r="K8" s="11">
+        <v>0.622</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="13"/>
-      <c r="B9" s="13"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13"/>
-      <c r="H9" s="13"/>
-      <c r="I9" s="13"/>
-      <c r="J9" s="13"/>
-      <c r="K9" s="13"/>
+      <c r="A9" s="12"/>
+      <c r="B9" s="12"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="12"/>
+      <c r="I9" s="12"/>
+      <c r="J9" s="12"/>
+      <c r="K9" s="12"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" s="13"/>
-      <c r="B10" s="13"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="13"/>
-      <c r="I10" s="13"/>
-      <c r="J10" s="13"/>
-      <c r="K10" s="13"/>
+      <c r="A10" s="12"/>
+      <c r="B10" s="12"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="12"/>
+      <c r="I10" s="12"/>
+      <c r="J10" s="12"/>
+      <c r="K10" s="12"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" s="13"/>
-      <c r="B11" s="13"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="13"/>
-      <c r="I11" s="13"/>
-      <c r="J11" s="13"/>
-      <c r="K11" s="13"/>
+      <c r="A11" s="12"/>
+      <c r="B11" s="12"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
+      <c r="H11" s="12"/>
+      <c r="I11" s="12"/>
+      <c r="J11" s="12"/>
+      <c r="K11" s="12"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12" s="13"/>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="13"/>
-      <c r="H12" s="13"/>
-      <c r="I12" s="13"/>
-      <c r="J12" s="13"/>
-      <c r="K12" s="13"/>
+      <c r="A12" s="12"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="12"/>
+      <c r="I12" s="12"/>
+      <c r="J12" s="12"/>
+      <c r="K12" s="12"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="13"/>
-      <c r="B13" s="13"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13"/>
-      <c r="H13" s="13"/>
-      <c r="I13" s="13"/>
-      <c r="J13" s="13"/>
-      <c r="K13" s="13"/>
+      <c r="A13" s="12"/>
+      <c r="B13" s="12"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="12"/>
+      <c r="I13" s="12"/>
+      <c r="J13" s="12"/>
+      <c r="K13" s="12"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" s="13"/>
-      <c r="B14" s="13"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="13"/>
-      <c r="H14" s="13"/>
-      <c r="I14" s="13"/>
-      <c r="J14" s="13"/>
-      <c r="K14" s="13"/>
+      <c r="A14" s="12"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="12"/>
+      <c r="I14" s="12"/>
+      <c r="J14" s="12"/>
+      <c r="K14" s="12"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" s="13"/>
-      <c r="B15" s="13"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="13"/>
-      <c r="H15" s="13"/>
-      <c r="I15" s="13"/>
-      <c r="J15" s="13"/>
-      <c r="K15" s="13"/>
+      <c r="A15" s="12"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="12"/>
+      <c r="I15" s="12"/>
+      <c r="J15" s="12"/>
+      <c r="K15" s="12"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A16" s="13"/>
-      <c r="B16" s="13"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="13"/>
-      <c r="G16" s="13"/>
-      <c r="H16" s="13"/>
-      <c r="I16" s="13"/>
-      <c r="J16" s="13"/>
-      <c r="K16" s="13"/>
+      <c r="A16" s="12"/>
+      <c r="B16" s="12"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="12"/>
+      <c r="H16" s="12"/>
+      <c r="I16" s="12"/>
+      <c r="J16" s="12"/>
+      <c r="K16" s="12"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A17" s="13"/>
-      <c r="B17" s="13"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13"/>
-      <c r="I17" s="13"/>
-      <c r="J17" s="13"/>
-      <c r="K17" s="13"/>
+      <c r="A17" s="12"/>
+      <c r="B17" s="12"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="12"/>
+      <c r="H17" s="12"/>
+      <c r="I17" s="12"/>
+      <c r="J17" s="12"/>
+      <c r="K17" s="12"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A18" s="13"/>
-      <c r="B18" s="13"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
-      <c r="I18" s="13"/>
-      <c r="J18" s="13"/>
-      <c r="K18" s="13"/>
+      <c r="A18" s="12"/>
+      <c r="B18" s="12"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="12"/>
+      <c r="J18" s="12"/>
+      <c r="K18" s="12"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A19" s="13"/>
-      <c r="B19" s="13"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="13"/>
-      <c r="I19" s="13"/>
-      <c r="J19" s="13"/>
-      <c r="K19" s="13"/>
+      <c r="A19" s="12"/>
+      <c r="B19" s="12"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="12"/>
+      <c r="I19" s="12"/>
+      <c r="J19" s="12"/>
+      <c r="K19" s="12"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A20" s="13"/>
-      <c r="B20" s="13"/>
-      <c r="C20" s="13"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="13"/>
-      <c r="H20" s="13"/>
-      <c r="I20" s="13"/>
-      <c r="J20" s="13"/>
-      <c r="K20" s="13"/>
+      <c r="A20" s="12"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="12"/>
+      <c r="I20" s="12"/>
+      <c r="J20" s="12"/>
+      <c r="K20" s="12"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A21" s="13"/>
-      <c r="B21" s="13"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
-      <c r="I21" s="13"/>
-      <c r="J21" s="13"/>
-      <c r="K21" s="13"/>
+      <c r="A21" s="12"/>
+      <c r="B21" s="12"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="12"/>
+      <c r="H21" s="12"/>
+      <c r="I21" s="12"/>
+      <c r="J21" s="12"/>
+      <c r="K21" s="12"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A22" s="13"/>
-      <c r="B22" s="13"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13"/>
-      <c r="G22" s="13"/>
-      <c r="H22" s="13"/>
-      <c r="I22" s="13"/>
-      <c r="J22" s="13"/>
-      <c r="K22" s="13"/>
+      <c r="A22" s="12"/>
+      <c r="B22" s="12"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="12"/>
+      <c r="H22" s="12"/>
+      <c r="I22" s="12"/>
+      <c r="J22" s="12"/>
+      <c r="K22" s="12"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A23" s="13"/>
-      <c r="B23" s="13"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
-      <c r="G23" s="13"/>
-      <c r="H23" s="13"/>
-      <c r="I23" s="13"/>
-      <c r="J23" s="13"/>
-      <c r="K23" s="13"/>
+      <c r="A23" s="12"/>
+      <c r="B23" s="12"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="12"/>
+      <c r="H23" s="12"/>
+      <c r="I23" s="12"/>
+      <c r="J23" s="12"/>
+      <c r="K23" s="12"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A24" s="13"/>
-      <c r="B24" s="13"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="13"/>
-      <c r="H24" s="13"/>
-      <c r="I24" s="13"/>
-      <c r="J24" s="13"/>
-      <c r="K24" s="13"/>
+      <c r="A24" s="12"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="12"/>
+      <c r="H24" s="12"/>
+      <c r="I24" s="12"/>
+      <c r="J24" s="12"/>
+      <c r="K24" s="12"/>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A25" s="13"/>
-      <c r="B25" s="13"/>
-      <c r="C25" s="13"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="13"/>
-      <c r="G25" s="13"/>
-      <c r="H25" s="13"/>
-      <c r="I25" s="13"/>
-      <c r="J25" s="13"/>
-      <c r="K25" s="13"/>
+      <c r="A25" s="12"/>
+      <c r="B25" s="12"/>
+      <c r="C25" s="12"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="12"/>
+      <c r="G25" s="12"/>
+      <c r="H25" s="12"/>
+      <c r="I25" s="12"/>
+      <c r="J25" s="12"/>
+      <c r="K25" s="12"/>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A26" s="13"/>
-      <c r="B26" s="13"/>
-      <c r="C26" s="13"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="13"/>
-      <c r="F26" s="13"/>
-      <c r="G26" s="13"/>
-      <c r="H26" s="13"/>
-      <c r="I26" s="13"/>
-      <c r="J26" s="13"/>
-      <c r="K26" s="13"/>
+      <c r="A26" s="12"/>
+      <c r="B26" s="12"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="12"/>
+      <c r="G26" s="12"/>
+      <c r="H26" s="12"/>
+      <c r="I26" s="12"/>
+      <c r="J26" s="12"/>
+      <c r="K26" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
